--- a/Result/checksun_type/太陽能電池模組.xlsx
+++ b/Result/checksun_type/太陽能電池模組.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>100.32</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>99.76</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>99.68</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>99.76000000000001</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>99.68000000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>64031.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>25053.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>25053.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>20848.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>25588.72</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>25588.72</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>3744.365424784759</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>64031</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>64031.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>98.88000000000001</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>99.52</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>99.73</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>99.52</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>99.73</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>36812.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>14985.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>14985.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>15586.0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>32703.8</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>32703.8</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>306.0413023357032</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>36812</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>36812.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>98.24000000000001</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>99.42</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>99.94</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>99.42</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>99.94</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>8495.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>12066.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>12066.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>15506.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>38344.86</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>38344.86</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1700.45891910351</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>8495</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>8495.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>98.08000000000001</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>99.54</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>100.03</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>99.54000000000001</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>100.03</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>8226.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>14445.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>14445</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>17200.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>39987.64</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>39987.64</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-1472.192845477262</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>8226</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>8226.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>98.22</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>99.53</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>100.19</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>99.53</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>100.19</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>7703.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>14823.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>14823.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>17899.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>42324.66</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>42324.66</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-1064.698710101293</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>7703</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>7703.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>98.47999999999999</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>99.51</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>100.38</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>99.51000000000001</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>100.38</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>13691.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>16643.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>16643</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>18149.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>44241.26</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>44241.26</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-388.5035627748621</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>13691</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>13691.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>99.02</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>99.57</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>100.51</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>99.56999999999999</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>100.51</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>22217.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>16186.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>16186.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>18551.8</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>44965.96</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>44965.96</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-50.20679649514568</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>22217</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>22217.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>99.22</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>99.42</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>100.61</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>99.42</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>100.61</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>20388.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>18946.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>18946.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>17549.6</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>46684.72</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>46684.72</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-478.6326019350054</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>20388</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>20388.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>99.19999999999999</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>99.39</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>100.71</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>99.39</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>100.71</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>10119.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>19956.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>19956.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>16534.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>47432.66</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>47432.66</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-877.6111596371302</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>10119</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>10119.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>99.3</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>99.34</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>100.76</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>99.34</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>100.76</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>16800.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>20976.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>20976</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>17568.3</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>49534.18</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>49534.18</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-315.9872720816966</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>16800</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>16800.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>99.3</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>99.26</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>100.9</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>100.9</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>11409.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>19656.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>19656.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>16650.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>53289.32</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>53289.32</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-218.2036015710146</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>11409</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>11409.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>34.47000000000001</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>35.99</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>38.93</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>127172359.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>36585325.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>36585325.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>38289467.3</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>56954942.76</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>56954942.76</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>6224892.673500799</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>127172359</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>127172359.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>33.85</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>36.02</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>39.04</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>36.02</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>39.04</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>8314392.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>19366910.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>19366910</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>27197241.7</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>56114087.56</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>56114087.56</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-1828923.629142936</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>8314392</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>8314392.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>34.27999999999999</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>36.22</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>39.24</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>36.22</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>39.24</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>14653318.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>38642909.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>38642909</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>28384991.3</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>57701178.02</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>57701178.02</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-534274.6104503088</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>14653318</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>14653318.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>34.85</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>36.5</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>39.45</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>39.45</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>19071114.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>39898162.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>39898162.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>28284523.7</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>62053830.94</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>62053830.94</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>655134.5809123777</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>19071114</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>19071114.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>35.22000000000001</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>36.76</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>39.64</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>36.76</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>39.64</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>13715445.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>40305071.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>40305071.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>27667110.2</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>62788123.4</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>62788123.4</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>1857557.619255062</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>13715445</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>13715445.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>35.63</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>36.99</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>39.8</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>39.8</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>41080281.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>39993609.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>39993609</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>27808761.6</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>63872216.82</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>63872216.82</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>4082785.151914071</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>41080281</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>41080281.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>36.04000000000001</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>37.24</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>39.97</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>37.24</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>39.97</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>104694387.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>35027573.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>35027573.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>25474156.8</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>66295486.98</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>66295486.98</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>4183921.157430012</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>104694387</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>104694387.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>36.02</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>37.4</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>40.14</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>40.14</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>20929585.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>18127073.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>18127073.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>16904264.4</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>67137973.94</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>67137973.94</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-2636821.661741149</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>20929585</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>20929585.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>36.25</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>37.54</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>40.28</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>37.54</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>40.28</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>21105658.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>16670885.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>16670885</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>17158051.0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>68819842.14</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>68819842.14</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-3311767.558352046</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>21105658</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>21105658.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>36.48999999999999</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>37.77</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>40.43</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>37.77</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>40.43</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>12158134.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>15029149.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>15029149.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>16316324.8</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>72715548.66</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>72715548.66</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-4176563.533569325</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>12158134</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>12158134.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>36.59</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>37.94</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>40.58</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>37.94</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>40.58</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>16250103.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>15623914.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>15623914.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>17160206.8</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>75441478.64</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>75441478.64</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-4304160.08625225</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>16250103</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>16250103.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>12.39</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>13.29</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>14.15</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>14.15</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>26119704.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>34501382.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>34501382</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>34609485.4</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>42902057.1</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>42902057.1</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-577637.104703553</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>26119704</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>26119704.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>12.45</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>13.39</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>14.18</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>14.18</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>35214902.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>40716516.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>40716516.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>34123731.5</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>43308539.52</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>43308539.52</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>203672.4769979939</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>35214902</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>35214902.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>12.63</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>14.22</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>14.22</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>43737691.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>41001956.8</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>41001956.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>32899981.8</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>43494788.36</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>43494788.36</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>338069.5052502751</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>43737691</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>43737691.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>12.93</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>13.62</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>14.27</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>14.27</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>33272234.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>36292512.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>36292512.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>30682542.9</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>43382880.32</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>43382880.32</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-395164.6152911186</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>33272234</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>33272234.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>13.14</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>13.7</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>14.32</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>14.32</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>34162379.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>34419396.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>34419396.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>28993242.5</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>43440651.04</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>43440651.04</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-307229.9440898597</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>34162379</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>34162379.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>13.26</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>13.78</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>14.36</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>14.36</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>57195376.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>34717588.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>34717588.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>28221070.3</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>43323447.32</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>43323447.32</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-266009.1657991186</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>57195376</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>57195376.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>13.41</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>13.85</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>14.4</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>14.4</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>36642104.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>27530946.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>27530946.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>25536290.6</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>42917345.92</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>42917345.92</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-2665443.119462393</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>36642104</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>36642104.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>13.45</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>13.89</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>14.43</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>14.43</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>20190471.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>24798006.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>24798006.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>26300943.2</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>42871371.14</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>42871371.14</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-3795875.227571983</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>20190471</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>20190471.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>13.44</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>13.92</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>14.45</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>14.45</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>23906651.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>25072573.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>25072573</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>29070275.6</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>43769603.24</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>43769603.24</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-3512536.302458107</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>23906651</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>23906651.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>13.51</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>13.97</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>14.49</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>14.49</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>35653342.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>23567088.8</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>23567088.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>31620576.3</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>44172918.42</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>44172918.42</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-3380480.82720764</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>35653342</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>35653342.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>13.63</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>14.01</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>14.53</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>14.53</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>21262165.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>21724551.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>21724551.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>37530399.8</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>45039926.82</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>45039926.82</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-4329672.725878127</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>21262165</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>21262165.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>15.42</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>16.18</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>16.83</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>16.83</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>14634.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>14548.8</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>14548.8</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>17818.7</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>29999.06</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>29999.06</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-2902.427356930613</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>14634</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>14634.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>15.37</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>16.84</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>16.84</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>12839.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>17159.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>17159</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>17915.0</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>30233.9</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>30233.9</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-3020.99928076757</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>12839</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>12839.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>15.43</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>16.37</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>16.87</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>16.87</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>10453.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>21846.8</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>21846.8</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>17928.2</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>30585.48</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>30585.48</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-2890.173483364375</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>10453</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>10453.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>15.66</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>16.48</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>16.92</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>16.92</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>16476.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>23074.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>23074.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>18946.2</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>30922.64</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>30922.64</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-2344.416148382516</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>16476</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>16476.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>15.9</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>16.58</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>16.96</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>16.96</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>18342.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>21525.8</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>21525.8</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>19455.3</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>30997.64</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>30997.64</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-2126.355093109058</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>18342</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>18342.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>16.08</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>16.65</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>16.99</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>16.99</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>27685.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>21088.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>21088.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>19477.0</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>31133.42</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>31133.42</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-1938.826617964503</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>27685</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>27685.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>16.29</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>16.74</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>17.03</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>17.03</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>36278.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>18671.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>18671</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>19526.2</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>31199.22</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>31199.22</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-2602.720702830695</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>36278</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>36278.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>16.39</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>16.8</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>17.05</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>17.05</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>16590.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>14009.6</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>14009.6</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>18938.3</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>31611.14</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>31611.14</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-4378.8650846813</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>16590</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>16590.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>16.37</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>16.82</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>17.07</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>17.07</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>8734.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>14818.2</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>14818.2</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>20712.1</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>32177.64</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>32177.64</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-4650.397591443547</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>8734</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>8734.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>16.33</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>16.85</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>17.09</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>17.09</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>16156.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>17384.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>17384.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>23754.9</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>32606.84</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>32606.84</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-4030.501258552344</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>16156</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>16156.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>16.35</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>16.86</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>17.12</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>17.12</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>15597.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>17865.4</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>17865.4</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>34457.9</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>32784.24</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>32784.24</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-3796.202880902329</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>15597</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>15597.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>100.96</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>108.88</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>116.13</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>108.88</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>116.13</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>507293.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>390648.2</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>390648.2</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>413482.5</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>1173198.42</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>1173198.42</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-65273.64825404435</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>507293</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>507293.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>100.06</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>110.12</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>116.12</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>110.12</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>116.12</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>370028.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>379489.6</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>379489.6</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>396910.1</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>1169863.72</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>1169863.72</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-81758.93193293636</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>370028</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>370028.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>99.2</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>111.22</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>116.13</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>111.22</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>116.13</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>304877.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>414526.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>414526.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>426922.8</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>1168955.64</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>1168955.64</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-87682.41104803438</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>304877</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>304877.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>99.3</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>112.68</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>116.22</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>112.68</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>116.22</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>383570.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>425777.0</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>425777</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>497277.9</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>1168885.06</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>1168885.06</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-86032.54510360176</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>383570</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>383570.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>100.24</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>114.31</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>116.34</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>114.31</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>116.34</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>387473.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>423142.2</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>423142.2</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>499779.7</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>1165775.88</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>1165775.88</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-89034.3957149979</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>387473</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>387473.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>101.14</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>115.74</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>116.41</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>115.74</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>116.41</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>451500.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>436316.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>436316.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>531910.4</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>1161801.62</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>1161801.62</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-90561.13245574245</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>451500</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>451500.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>102.74</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>117.36</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>116.56</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>117.36</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>116.56</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>545212.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>414330.6</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>414330.6</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>573471.0</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>1159595.78</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>1159595.78</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-96367.89449767256</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>545212</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>545212.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>103.9</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>118.62</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>116.62</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>118.62</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>116.62</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>361130.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>439319.2</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>439319.2</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>585928.9</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>1153377.78</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>1153377.78</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-111262.1297540844</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>361130</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>361130.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>105.0</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>119.62</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>116.59</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>119.62</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>116.59</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>370396.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>568778.8</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>568778.8</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>603621.1</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>1153337.92</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>1153337.92</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-108842.8897720267</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>370396</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>370396.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>107.4</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>120.78</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>116.56</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>120.78</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>116.56</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>453346.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>576417.2</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>576417.2</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>601468.9</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>1151585.72</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>1151585.72</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-102492.3723058006</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>453346</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>453346.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>109.9</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>121.72</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>116.54</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>116.54</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>341569.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>627504.0</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>627504</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>615295.8</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>1146810.3</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>1146810.3</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-98647.2626288418</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>341569</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>341569.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>293.9</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>314.2</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>313.06</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>314.2</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>313.06</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>215423673.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>178377059.2</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>178377059.2</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>203196614.5</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>342055488.44</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>342055488.44</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-29757059.1646015</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>215423673</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>215423673.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>291.3</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>315.35</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>312.95</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>315.35</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>312.95</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>145369311.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>201601517.0</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>201601517</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>213574610.4</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>341401273.88</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>341401273.88</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-33232461.61026913</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>145369311</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>145369311.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>291.4</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>316.75</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>313.05</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>316.75</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>313.05</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>255529988.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>235452704.8</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>235452704.8</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>262643830.0</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>341945859.18</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>341945859.18</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-29504624.11799899</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>255529988</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>255529988.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>294.4</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>318.42</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>313.22</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>318.42</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>313.22</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>148293165.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>208628721.4</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>208628721.4</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>273247364.4</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>345426351.54</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>345426351.54</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-34928335.08911312</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>148293165</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>148293165.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>298.2</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>319.8</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>313.4</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>319.8</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>313.4</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>127269159.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>208479663.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>208479663.4</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>276125257.9</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>349062466.22</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>349062466.22</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-29939393.47323638</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>127269159</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>127269159.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>301.5</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>320.95</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>313.2</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>320.95</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>313.2</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>331545962.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>228016169.8</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>228016169.8</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>310860645.9</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>348437711.32</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>348437711.32</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-19490497.8979398</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>331545962</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>331545962.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>306.4</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>322.75</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>313.15</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>322.75</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>313.15</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>314625250.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>225547703.8</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>225547703.8</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>318140668.5</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>344419428.18</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>344419428.18</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-25754215.32973254</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>314625250</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>314625250.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>310.2</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>324.27</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>312.96</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>324.27</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>312.96</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>121410071.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>289834955.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>289834955.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>319654840.6</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>340158543.92</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>340158543.92</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-31969656.25623173</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>121410071</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>121410071.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>315.5</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>325.05</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>312.53</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>325.05</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>312.53</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>147547875.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>337866007.4</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>337866007.4</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>378484318.3</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>339527483.9</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>339527483.9</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-19005457.82065082</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>147547875</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>147547875.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>320.4</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>326.12</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>312.18</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>326.12</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>312.18</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>224951691.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>343770852.4</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>343770852.4</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>476802600.5</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>340098445.2</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>340098445.2</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-2606886.990511954</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>224951691</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>224951691.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>325.1</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>326.8</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>311.79</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>326.8</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>311.79</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>319203632.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>393705122.0</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>393705122</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>465510492.3</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>339342581.32</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>339342581.32</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>12619479.87363327</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>319203632</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>319203632.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>37.85</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>37.02</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>38.29</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>37.02</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>38.29</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>8037228.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>11392391.8</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>11392391.8</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>20084395.9</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>16151911.48</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>16151911.48</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-1383545.27651977</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>8037228</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>8037228.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>37.32</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>36.94</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>38.34</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>38.34</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>10628180.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>12954854.0</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>12954854</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>24532755.6</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>16847558.98</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>16847558.98</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-796166.4008610174</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>10628180</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>10628180.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>37.04000000000001</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>36.88</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>38.42</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>36.88</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>38.42</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>11902511.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>16127111.2</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>16127111.2</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>26550692.9</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>17120094.2</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>17120094.2</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-206221.2070320509</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>11902511</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>11902511.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>37.37</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>36.91</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>38.52</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>36.91</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>38.52</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>12779530.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>20321683.0</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>20321683</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>26444349.0</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>17524907.22</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>17524907.22</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>507387.2201176211</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>12779530</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>12779530.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>37.39</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>36.9</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>38.64</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>38.64</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>13614510.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>24105989.6</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>24105989.6</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>25843980.8</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>17736209.48</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>17736209.48</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>1414740.536755808</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>13614510</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>13614510.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>37.7</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>36.93</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>38.74</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>36.93</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>38.74</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>15849539.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>28776400.0</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>28776400</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>25158334.3</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>18164918.46</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>18164918.46</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>2570970.969926223</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>15849539</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>15849539.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>38.21</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>37.07</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>38.9</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>37.07</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>38.9</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>26489466.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>36110657.2</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>36110657.2</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>24093162.2</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>18489161.22</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>18489161.22</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>3891440.94695802</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>26489466</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>26489466.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>37.98999999999999</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>37.07</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>39.04</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>37.07</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>39.04</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>32875370.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>36974274.6</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>36974274.6</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>22276259.0</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>18351541.4</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>18351541.4</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>4498854.416040663</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>32875370</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>32875370.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>37.16</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>36.98</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>39.16</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>36.98</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>39.16</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>31701063.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>32567015.0</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>32567015</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>20303587.6</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>18315126.16</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>18315126.16</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>4521710.571300123</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>31701063</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>31701063.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>36.71</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>36.99</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>39.3</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>39.3</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>36966562.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>27581972.0</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>27581972</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>17975214.7</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>18716874.7</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>18716874.7</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>4518691.165552922</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>36966562</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>36966562.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>36.11</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>36.92</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>39.4</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>36.92</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>39.4</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>52520825.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>21540268.6</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>21540268.6</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>15270788.0</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>18724302.9</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>18724302.9</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>3788835.294287179</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>52520825</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>52520825.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>12.04</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>13.29</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>14.27</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>14.27</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>4596524.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>6136300.4</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>6136300.4</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>7073001.0</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>30854093.86</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>30854093.86</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-2169313.085164293</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>4596524</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>4596524.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>12.04</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>13.43</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>14.23</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>14.23</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>6558890.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>6146868.2</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>6146868.2</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>7224979.7</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>30937402.4</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>30937402.4</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-2241455.818365904</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>6558890</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>6558890.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>12.13</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>13.58</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>14.21</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>14.21</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>4662006.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>6815781.6</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>6815781.6</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>7509790.3</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>31054367.72</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>31054367.72</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-2474718.372283708</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>4662006</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>4662006.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>12.38</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>13.76</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>14.2</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>7354036.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>7220126.2</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>7220126.2</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>7690258.5</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>31465637.78</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>31465637.78</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-2516330.221727583</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>7354036</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>7354036.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>12.61</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>14.2</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>7510046.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>8012093.6</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>8012093.6</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>7946348.3</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>31843794.6</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>31843794.6</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-2774338.570157131</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>7510046</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>7510046.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>12.88</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>14.17</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>14.17</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>14.17</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>4649363.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>8009701.6</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>8009701.6</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>8175667.5</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>31841882.54</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>31841882.54</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-3060553.76183659</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>4649363</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>4649363.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>13.2</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>14.36</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>14.15</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>14.15</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>9903457.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>8303091.2</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>8303091.2</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>8508648.8</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>32120796.14</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>32120796.14</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>-3053625.365598796</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>9903457</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>9903457.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>13.41</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>14.47</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>14.11</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>14.11</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>6683729.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>8203799.0</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>8203799</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>8613484.6</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>32261810.34</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>32261810.34</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>-3497608.250773417</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>6683729</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>6683729.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>13.54</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>14.54</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>14.04</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>14.04</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>11313873.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>8160390.8</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>8160390.8</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>8745779.5</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>32301013.08</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>32301013.08</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-3661984.077780968</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>11313873</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>11313873.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>13.64</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>14.63</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>13.98</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>13.98</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>7498086.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>7880603.0</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>7880603</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>8787115.8</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>32213809.44</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>32213809.44</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-4262108.399299579</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>7498086</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>7498086.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>13.72</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>14.71</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>13.92</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>13.92</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>6116311.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>8341633.4</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>8341633.4</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>9420617.8</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>32160012.06</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>32160012.06</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-4558376.380065465</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>6116311</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>6116311.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>20.69</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>21.32</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>22.55</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>1084.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>1556.4</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>1556.4</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>1397.5</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>7713.98</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>7713.98</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>-123.4651114306689</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>1084</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>1084.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>20.8</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>21.42</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>22.57</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>22.57</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>1537.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>1664.0</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>1664</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>1551.8</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>7792.22</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>7792.22</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>-101.7829228576081</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>1537</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>1537.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>20.97</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>21.52</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>22.59</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>21.52</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>22.59</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>1027.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>1582.0</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>1582</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>1531.6</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>7859.38</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>7859.38</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>-115.708977651178</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>1027</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>1027.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>21.17000000000001</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>21.66</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>22.61</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>22.61</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>3268.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>1537.2</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>1537.2</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>1506.4</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>7911.6</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>7911.6</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>-76.82802101159291</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>3268</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>3268.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>21.24</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>21.74</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>22.61</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>22.61</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>866.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>1140.0</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>1140</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>1353.6</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>8067.06</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>8067.06</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>-258.6470822046285</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>866</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>866.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>21.31</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>21.86</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>22.6</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>1622.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>1238.6</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>1238.6</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>1365.5</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>8109.52</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>8109.52</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>-251.7940595445143</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>1622</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>1622.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>21.38</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>21.98</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>22.58</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>22.58</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>1127.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>1439.6</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>1439.6</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>1347.6</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>8101.52</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>8101.52</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>-314.01138218919</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>1127</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>1127.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>21.38</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>22.1</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>22.56</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>803.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>1481.2</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>1481.2</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>1415.8</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>8133.46</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>8133.46</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>-338.642865174827</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>803</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>803.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>21.34</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>22.22</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>22.53</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>22.53</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>1282.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>1475.6</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>1475.6</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>1436.4</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>8169.96</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>8169.96</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>-327.0220242552073</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>1282</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>1282.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>21.38</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>22.35</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>22.51</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>22.35</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>22.51</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>1359.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>1567.2</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>1567.2</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>1435.4</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>8187.1</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>8187.1</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>-350.0628935037789</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>1359</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>1359.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>21.36</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>22.41</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>22.48</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>22.41</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>22.48</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>2627.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>1492.4</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>1492.4</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>1397.8</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>8535.92</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>8535.92</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>-378.7261748051747</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>2627</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>2627.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43627,11 @@
           <t>6.302</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>6.57</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>6.57</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>6.57</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43678,16 @@
           <t>36325854.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>29986849.0</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>29986849</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>24630382.5</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>39591305.02</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>39591305.02</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>-2561389.810234267</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>36325854</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>36325854.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>6.302</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>6.61</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>6.56</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>6.56</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>35567249.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>25618149.4</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>25618149.4</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>22763242.5</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>39659177.78</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>39659177.78</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>-3718653.028287549</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>35567249</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>35567249.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>6.311999999999999</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>6.65</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>6.56</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>6.56</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>15411559.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>22322327.0</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>22322327</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>22977296.1</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>39401062.22</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>39401062.22</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>-5157798.053067677</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>15411559</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>15411559.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>6.382</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>6.68</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>6.56</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>6.56</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>15720972.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>22981547.2</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>22981547.2</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>24041313.8</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>39535003.52</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>39535003.52</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>-4869974.229429729</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>15720972</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>15720972.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>6.426</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>6.68</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>6.56</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>6.56</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>46908611.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>24130138.2</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>24130138.2</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>25727178.5</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>39552729.94</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>39552729.94</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>-4318021.080324456</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>46908611</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>46908611.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>6.436</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>6.67</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>6.55</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>6.55</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>14482356.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>19273916.0</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>19273916</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>29106471.9</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>38877404.46</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>38877404.46</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>-6716834.293019626</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>14482356</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>14482356.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>6.67</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>6.55</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>6.55</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>19088137.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>19908335.6</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>19908335.6</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>32251761.1</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>38987992.86</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>38987992.86</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>-6429581.7649763</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>19088137</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>19088137.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,21 +46637,17 @@
           <t>6.529999999999999</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
+      <c r="AM108" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AO108" t="inlineStr">
         <is>
           <t>6.67</t>
         </is>
       </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>6.55</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>6.67</t>
-        </is>
-      </c>
       <c r="AP108" t="inlineStr">
         <is>
           <t>-101.03</t>
@@ -47328,20 +46688,16 @@
           <t>18707660.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>23632265.2</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>23632265.2</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>33228746.4</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>39121110.62</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>39121110.62</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>-6283069.626165252</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>18707660</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>18707660.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>6.56</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>6.65</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>6.54</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>6.54</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>21463927.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>25101080.4</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>25101080.4</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>35104960.6</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>39133211.8</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>39133211.8</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>-5808605.834072143</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>21463927</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>21463927.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>6.642</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>6.64</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>6.54</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>6.54</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>22627500.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>27324218.8</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>27324218.8</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>40925104.0</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>39344738.72</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>39344738.72</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>-5218664.529865123</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>22627500</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>22627500.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47927,11 @@
           <t>6.752</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>6.62</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>6.53</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>6.53</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47978,16 @@
           <t>17654454.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>38939027.8</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>38939027.8</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>44983471.9</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>39497281.48</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>39497281.48</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>-4314178.89778848</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>17654454</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>17654454.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48173,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48357,11 @@
           <t>94.96000000000001</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>102.36</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>107.79</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>102.36</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>107.79</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48408,16 @@
           <t>201371785.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>241585594.2</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>241585594.2</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>391104366.6</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>1504374242.12</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>1504374242.12</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48434,10 @@
           <t>-191018954.3335088</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>201371785</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>201371785.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48603,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48787,11 @@
           <t>94.44</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>102.57</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>108.73</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>102.57</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>108.73</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48838,16 @@
           <t>212282665.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>262256753.8</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>262256753.8</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>447757535.9</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>1569603789.94</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>1569603789.94</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48864,10 @@
           <t>-195652551.2250234</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>212282665</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>212282665.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49033,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49217,11 @@
           <t>94.5</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>102.92</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>109.43</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>102.92</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>109.43</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49268,16 @@
           <t>170614152.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>333387882.0</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>333387882</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>499097507.5</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>1622376544.82</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>1622376544.82</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49294,10 @@
           <t>-196453407.0977221</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>170614152</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>170614152.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49463,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49647,11 @@
           <t>96.08000000000001</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>103.4</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>110.12</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>110.12</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49698,16 @@
           <t>292246810.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>385454540.6</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>385454540.6</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>620641046.6</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>1711289280.24</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>1711289280.24</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49724,10 @@
           <t>-186116810.2695159</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>292246810</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>292246810.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49893,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50077,11 @@
           <t>98.64</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>103.88</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>110.9</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>103.88</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>110.9</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50128,16 @@
           <t>331412559.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>474610797.8</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>474610797.8</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>910559577.2</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>1764394296.32</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>1764394296.32</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50154,10 @@
           <t>-177735284.9338814</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>331412559</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>331412559.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50507,11 @@
           <t>100.48</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>104.12</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>111.46</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>104.12</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>111.46</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50558,16 @@
           <t>304727583.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>540623139.0</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>540623139</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>1033074216.6</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>1817944622.74</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>1817944622.74</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50584,10 @@
           <t>-163610318.8139077</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>304727583</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>304727583.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50753,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50937,11 @@
           <t>102.84</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>104.76</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>111.96</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>104.76</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>111.96</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50988,16 @@
           <t>567938306.0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>633258318.0</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>633258318</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>1216731969.7</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>1859281366.72</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>1859281366.72</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51014,10 @@
           <t>-134729465.5420202</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>567938306</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>567938306.0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51183,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51367,11 @@
           <t>104.5</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>104.82</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>112.56</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>104.82</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>112.56</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51418,16 @@
           <t>430947445.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>664807133.0</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>664807133</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>1501613925.2</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>1915776286.98</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>1915776286.98</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51444,10 @@
           <t>-116860485.9913944</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>430947445</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>430947445.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51613,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51797,11 @@
           <t>105.3</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>104.76</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>113.06</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>104.76</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>113.06</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51848,16 @@
           <t>738028096.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>855827552.6</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>855827552.6</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>1626976225.2</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>2024055315.18</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>2024055315.18</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51874,10 @@
           <t>-72482191.31223631</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>738028096</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>738028096.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52043,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52227,11 @@
           <t>107.3</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>104.83</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>113.53</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>104.83</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>113.53</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52278,16 @@
           <t>661474265.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>1346508356.6</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>1346508356.6</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>1613009835.6</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>2183695022.74</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>2183695022.74</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52304,10 @@
           <t>-39397476.11657333</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>661474265</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>661474265.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52473,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52657,11 @@
           <t>107.8</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>104.7</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>113.99</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>113.99</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52708,16 @@
           <t>767903478.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>1525525294.2</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>1525525294.2</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>1580511190.2</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>2239589271.02</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>2239589271.02</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52734,10 @@
           <t>17475651.63139415</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>767903478</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>767903478.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
@@ -53629,7 +52903,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -53813,15 +53087,11 @@
           <t>20.3</t>
         </is>
       </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>21.79</t>
-        </is>
-      </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>22.8</t>
-        </is>
+      <c r="AM123" t="n">
+        <v>21.79</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>22.8</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -53868,20 +53138,16 @@
           <t>1628674.0</t>
         </is>
       </c>
-      <c r="AX123" t="inlineStr">
-        <is>
-          <t>2059700.6</t>
-        </is>
+      <c r="AX123" t="n">
+        <v>2059700.6</v>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
           <t>2491565.4</t>
         </is>
       </c>
-      <c r="AZ123" t="inlineStr">
-        <is>
-          <t>3150800.86</t>
-        </is>
+      <c r="AZ123" t="n">
+        <v>3150800.86</v>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
@@ -53898,8 +53164,10 @@
           <t>-251785.1454102122</t>
         </is>
       </c>
-      <c r="BD123" t="n">
-        <v>1628674</v>
+      <c r="BD123" t="inlineStr">
+        <is>
+          <t>1628674.0</t>
+        </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
@@ -54065,7 +53333,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -54249,15 +53517,11 @@
           <t>20.14</t>
         </is>
       </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>21.89</t>
-        </is>
-      </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>22.86</t>
-        </is>
+      <c r="AM124" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>22.86</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -54304,20 +53568,16 @@
           <t>2734810.0</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
-        <is>
-          <t>2212603.8</t>
-        </is>
+      <c r="AX124" t="n">
+        <v>2212603.8</v>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
           <t>2555639.6</t>
         </is>
       </c>
-      <c r="AZ124" t="inlineStr">
-        <is>
-          <t>3206762.48</t>
-        </is>
+      <c r="AZ124" t="n">
+        <v>3206762.48</v>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
@@ -54334,8 +53594,10 @@
           <t>-212515.2384718382</t>
         </is>
       </c>
-      <c r="BD124" t="n">
-        <v>2734810</v>
+      <c r="BD124" t="inlineStr">
+        <is>
+          <t>2734810.0</t>
+        </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
@@ -54501,7 +53763,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -54685,15 +53947,11 @@
           <t>20.27</t>
         </is>
       </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>22.03</t>
-        </is>
-      </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>22.94</t>
-        </is>
+      <c r="AM125" t="n">
+        <v>22.03</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>22.94</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -54740,20 +53998,16 @@
           <t>2485175.0</t>
         </is>
       </c>
-      <c r="AX125" t="inlineStr">
-        <is>
-          <t>2390344.4</t>
-        </is>
+      <c r="AX125" t="n">
+        <v>2390344.4</v>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
           <t>2413867.6</t>
         </is>
       </c>
-      <c r="AZ125" t="inlineStr">
-        <is>
-          <t>3236344.22</t>
-        </is>
+      <c r="AZ125" t="n">
+        <v>3236344.22</v>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
@@ -54770,8 +54024,10 @@
           <t>-267340.1129001672</t>
         </is>
       </c>
-      <c r="BD125" t="n">
-        <v>2485175</v>
+      <c r="BD125" t="inlineStr">
+        <is>
+          <t>2485175.0</t>
+        </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
@@ -54937,7 +54193,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -55121,15 +54377,11 @@
           <t>20.65</t>
         </is>
       </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>22.22</t>
-        </is>
-      </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>23.05</t>
-        </is>
+      <c r="AM126" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>23.05</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -55176,20 +54428,16 @@
           <t>1352852.0</t>
         </is>
       </c>
-      <c r="AX126" t="inlineStr">
-        <is>
-          <t>2605038.8</t>
-        </is>
+      <c r="AX126" t="n">
+        <v>2605038.8</v>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
           <t>2417674.3</t>
         </is>
       </c>
-      <c r="AZ126" t="inlineStr">
-        <is>
-          <t>3249544.46</t>
-        </is>
+      <c r="AZ126" t="n">
+        <v>3249544.46</v>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
@@ -55206,8 +54454,10 @@
           <t>-309366.8937656311</t>
         </is>
       </c>
-      <c r="BD126" t="n">
-        <v>1352852</v>
+      <c r="BD126" t="inlineStr">
+        <is>
+          <t>1352852.0</t>
+        </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
@@ -55373,7 +54623,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -55557,15 +54807,11 @@
           <t>21.1</t>
         </is>
       </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>22.42</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>23.15</t>
-        </is>
+      <c r="AM127" t="n">
+        <v>22.42</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>23.15</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -55612,20 +54858,16 @@
           <t>2096992.0</t>
         </is>
       </c>
-      <c r="AX127" t="inlineStr">
-        <is>
-          <t>2840348.0</t>
-        </is>
+      <c r="AX127" t="n">
+        <v>2840348</v>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
           <t>2506700.4</t>
         </is>
       </c>
-      <c r="AZ127" t="inlineStr">
-        <is>
-          <t>3289694.68</t>
-        </is>
+      <c r="AZ127" t="n">
+        <v>3289694.68</v>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
@@ -55642,8 +54884,10 @@
           <t>-237036.0130818067</t>
         </is>
       </c>
-      <c r="BD127" t="n">
-        <v>2096992</v>
+      <c r="BD127" t="inlineStr">
+        <is>
+          <t>2096992.0</t>
+        </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
@@ -55809,7 +55053,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -55993,15 +55237,11 @@
           <t>21.57</t>
         </is>
       </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>22.65</t>
-        </is>
-      </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>23.26</t>
-        </is>
+      <c r="AM128" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>23.26</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -56048,20 +55288,16 @@
           <t>2393190.0</t>
         </is>
       </c>
-      <c r="AX128" t="inlineStr">
-        <is>
-          <t>2923430.2</t>
-        </is>
+      <c r="AX128" t="n">
+        <v>2923430.2</v>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
           <t>2522532.2</t>
         </is>
       </c>
-      <c r="AZ128" t="inlineStr">
-        <is>
-          <t>3310633.18</t>
-        </is>
+      <c r="AZ128" t="n">
+        <v>3310633.18</v>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
@@ -56078,8 +55314,10 @@
           <t>-204969.8973519928</t>
         </is>
       </c>
-      <c r="BD128" t="n">
-        <v>2393190</v>
+      <c r="BD128" t="inlineStr">
+        <is>
+          <t>2393190.0</t>
+        </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
@@ -56245,7 +55483,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -56429,15 +55667,11 @@
           <t>22.06</t>
         </is>
       </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>22.77</t>
-        </is>
-      </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>23.37</t>
-        </is>
+      <c r="AM129" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>23.37</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -56484,20 +55718,16 @@
           <t>3623513.0</t>
         </is>
       </c>
-      <c r="AX129" t="inlineStr">
-        <is>
-          <t>2898675.4</t>
-        </is>
+      <c r="AX129" t="n">
+        <v>2898675.4</v>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
           <t>2489443.7</t>
         </is>
       </c>
-      <c r="AZ129" t="inlineStr">
-        <is>
-          <t>3538964.48</t>
-        </is>
+      <c r="AZ129" t="n">
+        <v>3538964.48</v>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
@@ -56514,8 +55744,10 @@
           <t>-183576.3071182594</t>
         </is>
       </c>
-      <c r="BD129" t="n">
-        <v>3623513</v>
+      <c r="BD129" t="inlineStr">
+        <is>
+          <t>3623513.0</t>
+        </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
@@ -56681,7 +55913,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -56865,15 +56097,11 @@
           <t>22.32</t>
         </is>
       </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>22.86</t>
-        </is>
-      </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
+      <c r="AM130" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>23.45</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -56920,20 +56148,16 @@
           <t>3558647.0</t>
         </is>
       </c>
-      <c r="AX130" t="inlineStr">
-        <is>
-          <t>2437390.8</t>
-        </is>
+      <c r="AX130" t="n">
+        <v>2437390.8</v>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
           <t>2617368.7</t>
         </is>
       </c>
-      <c r="AZ130" t="inlineStr">
-        <is>
-          <t>3525621.92</t>
-        </is>
+      <c r="AZ130" t="n">
+        <v>3525621.92</v>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
@@ -56950,8 +56174,10 @@
           <t>-278278.0601015594</t>
         </is>
       </c>
-      <c r="BD130" t="n">
-        <v>3558647</v>
+      <c r="BD130" t="inlineStr">
+        <is>
+          <t>3558647.0</t>
+        </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
@@ -57117,7 +56343,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -57301,15 +56527,11 @@
           <t>22.42</t>
         </is>
       </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>22.91</t>
-        </is>
-      </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>23.51</t>
-        </is>
+      <c r="AM131" t="n">
+        <v>22.91</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>23.51</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -57356,20 +56578,16 @@
           <t>2529398.0</t>
         </is>
       </c>
-      <c r="AX131" t="inlineStr">
-        <is>
-          <t>2230309.8</t>
-        </is>
+      <c r="AX131" t="n">
+        <v>2230309.8</v>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
           <t>2586744.3</t>
         </is>
       </c>
-      <c r="AZ131" t="inlineStr">
-        <is>
-          <t>3501325.56</t>
-        </is>
+      <c r="AZ131" t="n">
+        <v>3501325.56</v>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
@@ -57386,8 +56604,10 @@
           <t>-396677.8479312179</t>
         </is>
       </c>
-      <c r="BD131" t="n">
-        <v>2529398</v>
+      <c r="BD131" t="inlineStr">
+        <is>
+          <t>2529398.0</t>
+        </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
@@ -57553,7 +56773,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -57737,15 +56957,11 @@
           <t>22.46</t>
         </is>
       </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>22.94</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>23.56</t>
-        </is>
+      <c r="AM132" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>23.56</v>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
@@ -57792,20 +57008,16 @@
           <t>2512403.0</t>
         </is>
       </c>
-      <c r="AX132" t="inlineStr">
-        <is>
-          <t>2173052.8</t>
-        </is>
+      <c r="AX132" t="n">
+        <v>2173052.8</v>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
           <t>2454817.9</t>
         </is>
       </c>
-      <c r="AZ132" t="inlineStr">
-        <is>
-          <t>3528900.16</t>
-        </is>
+      <c r="AZ132" t="n">
+        <v>3528900.16</v>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
@@ -57822,8 +57034,10 @@
           <t>-441376.6574046155</t>
         </is>
       </c>
-      <c r="BD132" t="n">
-        <v>2512403</v>
+      <c r="BD132" t="inlineStr">
+        <is>
+          <t>2512403.0</t>
+        </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
@@ -57989,7 +57203,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -58173,15 +57387,11 @@
           <t>22.5</t>
         </is>
       </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>22.93</t>
-        </is>
-      </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>23.62</t>
-        </is>
+      <c r="AM133" t="n">
+        <v>22.93</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>23.62</v>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
@@ -58228,20 +57438,16 @@
           <t>2269416.0</t>
         </is>
       </c>
-      <c r="AX133" t="inlineStr">
-        <is>
-          <t>2121634.2</t>
-        </is>
+      <c r="AX133" t="n">
+        <v>2121634.2</v>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
           <t>2354852.6</t>
         </is>
       </c>
-      <c r="AZ133" t="inlineStr">
-        <is>
-          <t>3601848.8</t>
-        </is>
+      <c r="AZ133" t="n">
+        <v>3601848.8</v>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
@@ -58258,8 +57464,10 @@
           <t>-487647.7546021617</t>
         </is>
       </c>
-      <c r="BD133" t="n">
-        <v>2269416</v>
+      <c r="BD133" t="inlineStr">
+        <is>
+          <t>2269416.0</t>
+        </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
